--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_aysen.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:46</t>
+    <t xml:space="preserve">2026-09-24 00:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -546,13 +546,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="3">
@@ -572,10 +572,10 @@
         <v>-0.31</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="4">
@@ -592,13 +592,13 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="5">
@@ -609,7 +609,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>10</v>
@@ -618,10 +618,10 @@
         <v>0.22</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="6">
@@ -641,10 +641,10 @@
         <v>0.32</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="7">
@@ -655,19 +655,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="8">
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="9">
@@ -701,19 +701,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="10">
@@ -730,13 +730,13 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="11">
@@ -747,19 +747,19 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="12">
@@ -776,13 +776,13 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.84</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="13">
@@ -793,19 +793,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="14">
@@ -822,13 +822,13 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="15">
@@ -839,16 +839,16 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="F15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.01</v>
@@ -871,7 +871,7 @@
         <v>0.15</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.06</v>
@@ -885,16 +885,16 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>-0.57</v>
@@ -917,10 +917,10 @@
         <v>-0.41</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_aysen.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:36</t>
+    <t xml:space="preserve">2026-10-01 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_aysen.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:08</t>
+    <t xml:space="preserve">2026-10-05 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
